--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -935,52 +935,49 @@
     <t>214</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>R$ 9.286,75</t>
-  </si>
-  <si>
-    <t>98.3</t>
-  </si>
-  <si>
-    <t>66.2</t>
-  </si>
-  <si>
-    <t>5.91</t>
-  </si>
-  <si>
-    <t>21.7</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>31.8%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
+    <t>36</t>
+  </si>
+  <si>
+    <t>R$ 8.884,97</t>
+  </si>
+  <si>
+    <t>94.3</t>
+  </si>
+  <si>
+    <t>65.5</t>
+  </si>
+  <si>
+    <t>6.09</t>
+  </si>
+  <si>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>33.4%</t>
+  </si>
+  <si>
+    <t>17.2%</t>
   </si>
   <si>
     <t>0.9%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
+    <t>6.5%</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -989,40 +986,40 @@
     <t>5.7%</t>
   </si>
   <si>
-    <t>2115.0</t>
-  </si>
-  <si>
-    <t>1709.0</t>
-  </si>
-  <si>
-    <t>87.0</t>
+    <t>2224.0</t>
+  </si>
+  <si>
+    <t>1799.0</t>
+  </si>
+  <si>
+    <t>94.0</t>
   </si>
   <si>
     <t>26.0</t>
   </si>
   <si>
-    <t>378.0</t>
-  </si>
-  <si>
-    <t>126.0</t>
+    <t>389.0</t>
+  </si>
+  <si>
+    <t>133.0</t>
   </si>
   <si>
     <t>17.0</t>
   </si>
   <si>
-    <t>636.0</t>
-  </si>
-  <si>
-    <t>247.0</t>
-  </si>
-  <si>
-    <t>576.0</t>
+    <t>676.0</t>
+  </si>
+  <si>
+    <t>265.0</t>
+  </si>
+  <si>
+    <t>601.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>48.0</t>
+    <t>49.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3121,7 +3118,9 @@
       <c r="N12" s="6">
         <v>175</v>
       </c>
-      <c r="O12" s="6"/>
+      <c r="O12" s="6">
+        <v>138</v>
+      </c>
       <c r="P12" s="7">
         <v>4.3985465116279068</v>
       </c>
@@ -3131,31 +3130,75 @@
       <c r="R12" s="8">
         <v>7.0117796992481205</v>
       </c>
-      <c r="S12" s="8"/>
+      <c r="S12" s="8">
+        <v>7</v>
+      </c>
       <c r="T12" s="9">
         <v>0.20289855072463769</v>
       </c>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="6"/>
-      <c r="AL12" s="6"/>
-      <c r="AM12" s="6"/>
-      <c r="AN12" s="9"/>
-      <c r="AO12" s="6"/>
+      <c r="U12" s="9">
+        <v>0.25362318840579712</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0.036231884057971016</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0.028985507246376812</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0.036231884057971016</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>47</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>35</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="6">
+        <v>12</v>
+      </c>
+      <c r="AM12" s="6">
+        <v>18</v>
+      </c>
+      <c r="AN12" s="9">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="AO12" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP12" s="4">
         <v>58</v>
       </c>
@@ -5328,7 +5371,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5358,14 +5401,26 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
+      <c r="M27" s="5">
+        <v>7627.6899999999996</v>
+      </c>
+      <c r="N27" s="6">
+        <v>70</v>
+      </c>
       <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
+      <c r="P27" s="7">
+        <v>5.5073814285714286</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>20.712392307692308</v>
+      </c>
+      <c r="R27" s="8">
+        <v>7.037179487179487</v>
+      </c>
       <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
+      <c r="T27" s="9">
+        <v>0.23076923076923078</v>
+      </c>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -7034,7 +7089,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7064,35 +7119,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>8480.75</v>
+      </c>
+      <c r="N39" s="6">
+        <v>91</v>
+      </c>
+      <c r="O39" s="6">
+        <v>56</v>
+      </c>
+      <c r="P39" s="7">
+        <v>3.2839011363636361</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>15.408630357142856</v>
+      </c>
+      <c r="R39" s="8">
+        <v>5.9204081632653063</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.48214285714285715</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.23214285714285715</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.16071428571428573</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>9</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7546,7 +7659,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7576,14 +7689,26 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
+      <c r="M43" s="5">
+        <v>10237.200000000001</v>
+      </c>
+      <c r="N43" s="6">
+        <v>90</v>
+      </c>
       <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
+      <c r="P43" s="7">
+        <v>11.889560439560441</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>28.964734782608698</v>
+      </c>
+      <c r="R43" s="8">
+        <v>9.3499999999999996</v>
+      </c>
       <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
+      <c r="T43" s="9">
+        <v>0.057971014492753624</v>
+      </c>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
@@ -7959,7 +8084,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -7987,14 +8112,26 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
+      <c r="M46" s="5">
+        <v>9646.3999999999996</v>
+      </c>
+      <c r="N46" s="6">
+        <v>110</v>
+      </c>
       <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
+      <c r="P46" s="7">
+        <v>3.1669811320754717</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>18.806189999999997</v>
+      </c>
+      <c r="R46" s="8">
+        <v>8.3869042857142855</v>
+      </c>
       <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
+      <c r="T46" s="9">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="U46" s="9"/>
       <c r="V46" s="9"/>
       <c r="W46" s="9"/>
@@ -8523,7 +8660,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8553,35 +8690,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>6839.8699999999999</v>
+      </c>
+      <c r="N50" s="6">
+        <v>81</v>
+      </c>
+      <c r="O50" s="6">
+        <v>51</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.6732063291139241</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>13.683333333333334</v>
+      </c>
+      <c r="R50" s="8">
+        <v>3.1123340000000002</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -9190,7 +9385,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9220,14 +9415,26 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
+      <c r="M55" s="5">
+        <v>5640.3999999999996</v>
+      </c>
+      <c r="N55" s="6">
+        <v>68</v>
+      </c>
       <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
+      <c r="P55" s="7">
+        <v>3.9068070422535213</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>49.247115384615384</v>
+      </c>
+      <c r="R55" s="8">
+        <v>38.469230769230769</v>
+      </c>
       <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
+      <c r="T55" s="9">
+        <v>0.019230769230769232</v>
+      </c>
       <c r="U55" s="9"/>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
@@ -10167,7 +10374,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -10197,14 +10404,26 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
+      <c r="M62" s="5">
+        <v>8435.2800000000007</v>
+      </c>
+      <c r="N62" s="6">
+        <v>81</v>
+      </c>
       <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
+      <c r="P62" s="7">
+        <v>3.0720879518072293</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>14.80673076923077</v>
+      </c>
+      <c r="R62" s="8">
+        <v>4.8700000000000001</v>
+      </c>
       <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
+      <c r="T62" s="9">
+        <v>0.67307692307692313</v>
+      </c>
       <c r="U62" s="9"/>
       <c r="V62" s="9"/>
       <c r="W62" s="9"/>
@@ -11458,7 +11677,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11486,14 +11705,26 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
+      <c r="M71" s="5">
+        <v>9824.2700000000004</v>
+      </c>
+      <c r="N71" s="6">
+        <v>104</v>
+      </c>
       <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
+      <c r="P71" s="7">
+        <v>4.5663303030303029</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>17.166059999999998</v>
+      </c>
+      <c r="R71" s="8">
+        <v>5.1432092592592591</v>
+      </c>
       <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
+      <c r="T71" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U71" s="9"/>
       <c r="V71" s="9"/>
       <c r="W71" s="9"/>
@@ -11962,7 +12193,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11992,14 +12223,26 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
+      <c r="M75" s="5">
+        <v>5306.04</v>
+      </c>
+      <c r="N75" s="6">
+        <v>58</v>
+      </c>
       <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
+      <c r="P75" s="7">
+        <v>4.6099421052631584</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>15.743332000000001</v>
+      </c>
+      <c r="R75" s="8">
+        <v>4.6576374999999999</v>
+      </c>
       <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
+      <c r="T75" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U75" s="9"/>
       <c r="V75" s="9"/>
       <c r="W75" s="9"/>
@@ -13507,7 +13750,7 @@
         <v>19688</v>
       </c>
       <c r="B86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C86" s="4">
         <v>51</v>
@@ -13537,35 +13780,93 @@
         <v>58</v>
       </c>
       <c r="L86" s="4"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="6"/>
-      <c r="O86" s="6"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="8"/>
-      <c r="R86" s="8"/>
-      <c r="S86" s="8"/>
-      <c r="T86" s="9"/>
-      <c r="U86" s="9"/>
-      <c r="V86" s="9"/>
-      <c r="W86" s="9"/>
-      <c r="X86" s="9"/>
-      <c r="Y86" s="9"/>
-      <c r="Z86" s="9"/>
-      <c r="AA86" s="9"/>
-      <c r="AB86" s="9"/>
-      <c r="AC86" s="9"/>
-      <c r="AD86" s="6"/>
-      <c r="AE86" s="6"/>
-      <c r="AF86" s="6"/>
-      <c r="AG86" s="6"/>
-      <c r="AH86" s="6"/>
-      <c r="AI86" s="6"/>
-      <c r="AJ86" s="6"/>
-      <c r="AK86" s="6"/>
-      <c r="AL86" s="6"/>
-      <c r="AM86" s="6"/>
-      <c r="AN86" s="9"/>
-      <c r="AO86" s="6"/>
+      <c r="M86" s="5">
+        <v>10056.040000000001</v>
+      </c>
+      <c r="N86" s="6">
+        <v>99</v>
+      </c>
+      <c r="O86" s="6">
+        <v>69</v>
+      </c>
+      <c r="P86" s="7">
+        <v>12.948989898989899</v>
+      </c>
+      <c r="Q86" s="8">
+        <v>28.789613043478262</v>
+      </c>
+      <c r="R86" s="8">
+        <v>7.2873134328358207</v>
+      </c>
+      <c r="S86" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="T86" s="9">
+        <v>0.057971014492753624</v>
+      </c>
+      <c r="U86" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="V86" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="W86" s="9">
+        <v>0</v>
+      </c>
+      <c r="X86" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="Y86" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="Z86" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="9">
+        <v>0.10144927536231885</v>
+      </c>
+      <c r="AB86" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="AC86" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE86" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF86" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG86" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI86" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ86" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL86" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM86" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP86" s="4">
         <v>58</v>
       </c>
@@ -14015,7 +14316,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -14045,14 +14346,26 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
+      <c r="M90" s="5">
+        <v>7605.3000000000002</v>
+      </c>
+      <c r="N90" s="6">
+        <v>80</v>
+      </c>
       <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
+      <c r="P90" s="7">
+        <v>7.8972912500000003</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>29.30462962962963</v>
+      </c>
+      <c r="R90" s="8">
+        <v>15.317628846153847</v>
+      </c>
       <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
+      <c r="T90" s="9">
+        <v>0.07407407407407407</v>
+      </c>
       <c r="U90" s="9"/>
       <c r="V90" s="9"/>
       <c r="W90" s="9"/>
@@ -16754,7 +17067,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>51</v>
@@ -16782,14 +17095,26 @@
         <v>58</v>
       </c>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
+      <c r="M109" s="5">
+        <v>10766.41</v>
+      </c>
+      <c r="N109" s="6">
+        <v>114</v>
+      </c>
       <c r="O109" s="6"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
+      <c r="P109" s="7">
+        <v>5.0401452173913048</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>21.538506896551727</v>
+      </c>
+      <c r="R109" s="8">
+        <v>8.2580448275862075</v>
+      </c>
       <c r="S109" s="8"/>
-      <c r="T109" s="9"/>
+      <c r="T109" s="9">
+        <v>0.20689655172413793</v>
+      </c>
       <c r="U109" s="9"/>
       <c r="V109" s="9"/>
       <c r="W109" s="9"/>
@@ -19177,7 +19502,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -19207,35 +19532,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>4379.71</v>
+      </c>
+      <c r="N126" s="6">
+        <v>49</v>
+      </c>
+      <c r="O126" s="6">
+        <v>31</v>
+      </c>
+      <c r="P126" s="7">
+        <v>7.7217693877551019</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>32.736022580645162</v>
+      </c>
+      <c r="R126" s="8">
+        <v>19.246109999999998</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>7</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -22606,7 +22989,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>51</v>
@@ -22636,14 +23019,26 @@
         <v>58</v>
       </c>
       <c r="L149" s="4"/>
-      <c r="M149" s="5"/>
-      <c r="N149" s="6"/>
+      <c r="M149" s="5">
+        <v>9984.2399999999998</v>
+      </c>
+      <c r="N149" s="6">
+        <v>129</v>
+      </c>
       <c r="O149" s="6"/>
-      <c r="P149" s="7"/>
-      <c r="Q149" s="8"/>
-      <c r="R149" s="8"/>
+      <c r="P149" s="7">
+        <v>24.886466165413534</v>
+      </c>
+      <c r="Q149" s="8">
+        <v>77.362451724137927</v>
+      </c>
+      <c r="R149" s="8">
+        <v>62.44140927835052</v>
+      </c>
       <c r="S149" s="8"/>
-      <c r="T149" s="9"/>
+      <c r="T149" s="9">
+        <v>0.022988505747126436</v>
+      </c>
       <c r="U149" s="9"/>
       <c r="V149" s="9"/>
       <c r="W149" s="9"/>
@@ -24391,7 +24786,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24421,14 +24816,26 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
+      <c r="M162" s="5">
+        <v>10386.83</v>
+      </c>
+      <c r="N162" s="6">
+        <v>101</v>
+      </c>
       <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
+      <c r="P162" s="7">
+        <v>8.9496567010309285</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>21.324242424242424</v>
+      </c>
+      <c r="R162" s="8">
+        <v>3.5963531249999998</v>
+      </c>
       <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
+      <c r="T162" s="9">
+        <v>0.12121212121212122</v>
+      </c>
       <c r="U162" s="9"/>
       <c r="V162" s="9"/>
       <c r="W162" s="9"/>
@@ -26314,7 +26721,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26344,14 +26751,26 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
+      <c r="M175" s="5">
+        <v>4853.4899999999998</v>
+      </c>
+      <c r="N175" s="6">
+        <v>68</v>
+      </c>
       <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
+      <c r="P175" s="7">
+        <v>7.505290476190476</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>18.05095142857143</v>
+      </c>
+      <c r="R175" s="8">
+        <v>3.0247484848484847</v>
+      </c>
       <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
+      <c r="T175" s="9">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="U175" s="9"/>
       <c r="V175" s="9"/>
       <c r="W175" s="9"/>
@@ -26413,7 +26832,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>51</v>
@@ -26441,14 +26860,26 @@
         <v>58</v>
       </c>
       <c r="L176" s="4"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="6"/>
+      <c r="M176" s="5">
+        <v>2829.8000000000002</v>
+      </c>
+      <c r="N176" s="6">
+        <v>31</v>
+      </c>
       <c r="O176" s="6"/>
-      <c r="P176" s="7"/>
-      <c r="Q176" s="8"/>
-      <c r="R176" s="8"/>
+      <c r="P176" s="7">
+        <v>2.9421875000000002</v>
+      </c>
+      <c r="Q176" s="8">
+        <v>17.819793749999999</v>
+      </c>
+      <c r="R176" s="8">
+        <v>7.8260437500000002</v>
+      </c>
       <c r="S176" s="8"/>
-      <c r="T176" s="9"/>
+      <c r="T176" s="9">
+        <v>0.3125</v>
+      </c>
       <c r="U176" s="9"/>
       <c r="V176" s="9"/>
       <c r="W176" s="9"/>
@@ -26977,7 +27408,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -27007,14 +27438,26 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
+      <c r="M180" s="5">
+        <v>3078.4499999999998</v>
+      </c>
+      <c r="N180" s="6">
+        <v>40</v>
+      </c>
       <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
+      <c r="P180" s="7">
+        <v>5.1273138888888887</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>30.50714285714286</v>
+      </c>
+      <c r="R180" s="8">
+        <v>16.245235714285716</v>
+      </c>
       <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
+      <c r="T180" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U180" s="9"/>
       <c r="V180" s="9"/>
       <c r="W180" s="9"/>
@@ -27076,7 +27519,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -27106,35 +27549,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>4732.8999999999996</v>
+      </c>
+      <c r="N181" s="6">
+        <v>44</v>
+      </c>
+      <c r="O181" s="6">
+        <v>22</v>
+      </c>
+      <c r="P181" s="7">
+        <v>4.2544444444444443</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>12.111363636363636</v>
+      </c>
+      <c r="R181" s="8">
+        <v>0.92888666666666664</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27902,7 +28403,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27932,35 +28433,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>2249.0999999999999</v>
+      </c>
+      <c r="N187" s="6">
+        <v>30</v>
+      </c>
+      <c r="O187" s="6">
+        <v>25</v>
+      </c>
+      <c r="P187" s="7">
+        <v>8.5166666666666675</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>22.877332000000003</v>
+      </c>
+      <c r="R187" s="8">
+        <v>8.7763875000000002</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -28158,7 +28717,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -28188,14 +28747,26 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
+      <c r="M189" s="5">
+        <v>6583.6099999999997</v>
+      </c>
+      <c r="N189" s="6">
+        <v>81</v>
+      </c>
       <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
+      <c r="P189" s="7">
+        <v>5.5866259259259259</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>35.461904285714283</v>
+      </c>
+      <c r="R189" s="8">
+        <v>28.181355932203392</v>
+      </c>
       <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
+      <c r="T189" s="9">
+        <v>0.27142857142857141</v>
+      </c>
       <c r="U189" s="9"/>
       <c r="V189" s="9"/>
       <c r="W189" s="9"/>
@@ -28257,7 +28828,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28287,14 +28858,26 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
+      <c r="M190" s="5">
+        <v>4997.8900000000003</v>
+      </c>
+      <c r="N190" s="6">
+        <v>65</v>
+      </c>
       <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
+      <c r="P190" s="7">
+        <v>3.6816934426229508</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>16.611332000000001</v>
+      </c>
+      <c r="R190" s="8">
+        <v>5.8902791666666667</v>
+      </c>
       <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
+      <c r="T190" s="9">
+        <v>0.76000000000000001</v>
+      </c>
       <c r="U190" s="9"/>
       <c r="V190" s="9"/>
       <c r="W190" s="9"/>
@@ -29610,7 +30193,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29640,35 +30223,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>5729.2600000000002</v>
+      </c>
+      <c r="N199" s="6">
+        <v>56</v>
+      </c>
+      <c r="O199" s="6">
+        <v>22</v>
+      </c>
+      <c r="P199" s="7">
+        <v>5.2380946428571429</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>13.963636363636363</v>
+      </c>
+      <c r="R199" s="8">
+        <v>1.8977272727272727</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -29709,7 +30350,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29739,14 +30380,26 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
+      <c r="M200" s="5">
+        <v>2438.48</v>
+      </c>
+      <c r="N200" s="6">
+        <v>25</v>
+      </c>
       <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
+      <c r="P200" s="7">
+        <v>16.733332000000001</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>24.211108333333332</v>
+      </c>
+      <c r="R200" s="8">
+        <v>3</v>
+      </c>
       <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
+      <c r="T200" s="9">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="U200" s="9"/>
       <c r="V200" s="9"/>
       <c r="W200" s="9"/>
@@ -30320,7 +30973,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>51</v>
@@ -30350,14 +31003,26 @@
         <v>58</v>
       </c>
       <c r="L205" s="4"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="6"/>
+      <c r="M205" s="5">
+        <v>3478.6799999999998</v>
+      </c>
+      <c r="N205" s="6">
+        <v>45</v>
+      </c>
       <c r="O205" s="6"/>
-      <c r="P205" s="7"/>
-      <c r="Q205" s="8"/>
-      <c r="R205" s="8"/>
+      <c r="P205" s="7">
+        <v>5.3948155555555548</v>
+      </c>
+      <c r="Q205" s="8">
+        <v>15.224446666666667</v>
+      </c>
+      <c r="R205" s="8">
+        <v>3.3066666666666666</v>
+      </c>
       <c r="S205" s="8"/>
-      <c r="T205" s="9"/>
+      <c r="T205" s="9">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="U205" s="9"/>
       <c r="V205" s="9"/>
       <c r="W205" s="9"/>
@@ -30419,7 +31084,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -30449,14 +31114,26 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
+      <c r="M206" s="5">
+        <v>3750.5</v>
+      </c>
+      <c r="N206" s="6">
+        <v>41</v>
+      </c>
       <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
+      <c r="P206" s="7">
+        <v>10.616667441860466</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>23.307938095238097</v>
+      </c>
+      <c r="R206" s="8">
+        <v>7.6212944444444446</v>
+      </c>
       <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
+      <c r="T206" s="9">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="U206" s="9"/>
       <c r="V206" s="9"/>
       <c r="W206" s="9"/>
@@ -31575,52 +32252,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
+        <v>319</v>
+      </c>
+      <c t="s" r="AA216" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="AB216" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AC216" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AD216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AJ216" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AK216" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AL216" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AM216" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AN216" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AO216" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AO216" s="11">
-        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -31637,10 +32314,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 8.884,97</t>
-  </si>
-  <si>
-    <t>94.3</t>
-  </si>
-  <si>
-    <t>65.5</t>
-  </si>
-  <si>
-    <t>6.09</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R$ 8.869,39</t>
+  </si>
+  <si>
+    <t>94.2</t>
+  </si>
+  <si>
+    <t>62.9</t>
+  </si>
+  <si>
+    <t>6.10</t>
   </si>
   <si>
     <t>22.1</t>
@@ -956,67 +956,70 @@
     <t>9.9</t>
   </si>
   <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>33.4%</t>
-  </si>
-  <si>
-    <t>17.2%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>30.8%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>6.5%</t>
+    <t>6.2%</t>
   </si>
   <si>
     <t>2.5%</t>
   </si>
   <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>2224.0</t>
-  </si>
-  <si>
-    <t>1799.0</t>
-  </si>
-  <si>
-    <t>94.0</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>389.0</t>
-  </si>
-  <si>
-    <t>133.0</t>
-  </si>
-  <si>
-    <t>17.0</t>
-  </si>
-  <si>
-    <t>676.0</t>
-  </si>
-  <si>
-    <t>265.0</t>
-  </si>
-  <si>
-    <t>601.0</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>2484.0</t>
+  </si>
+  <si>
+    <t>2031.0</t>
+  </si>
+  <si>
+    <t>113.0</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>416.0</t>
+  </si>
+  <si>
+    <t>141.0</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>711.0</t>
+  </si>
+  <si>
+    <t>287.0</t>
+  </si>
+  <si>
+    <t>749.0</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>49.0</t>
@@ -5407,7 +5410,9 @@
       <c r="N27" s="6">
         <v>70</v>
       </c>
-      <c r="O27" s="6"/>
+      <c r="O27" s="6">
+        <v>41</v>
+      </c>
       <c r="P27" s="7">
         <v>5.5073814285714286</v>
       </c>
@@ -5417,31 +5422,75 @@
       <c r="R27" s="8">
         <v>7.037179487179487</v>
       </c>
-      <c r="S27" s="8"/>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
       <c r="T27" s="9">
         <v>0.23076923076923078</v>
       </c>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="U27" s="9">
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -7144,13 +7193,13 @@
         <v>0.48214285714285715</v>
       </c>
       <c r="U39" s="9">
-        <v>0.23214285714285715</v>
+        <v>0.25</v>
       </c>
       <c r="V39" s="9">
         <v>0.035714285714285712</v>
       </c>
       <c r="W39" s="9">
-        <v>0</v>
+        <v>0.017857142857000002</v>
       </c>
       <c r="X39" s="9">
         <v>0.017857142857142856</v>
@@ -7174,13 +7223,13 @@
         <v>14</v>
       </c>
       <c r="AE39" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF39" s="6">
         <v>2</v>
       </c>
       <c r="AG39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="6">
         <v>1</v>
@@ -7560,7 +7609,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7590,35 +7639,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>11721.98</v>
+      </c>
+      <c r="N42" s="6">
+        <v>132</v>
+      </c>
+      <c r="O42" s="6">
+        <v>90</v>
+      </c>
+      <c r="P42" s="7">
+        <v>7.6997418604651164</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>27.200925555555553</v>
+      </c>
+      <c r="R42" s="8">
+        <v>11.746255056179775</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -7695,7 +7802,9 @@
       <c r="N43" s="6">
         <v>90</v>
       </c>
-      <c r="O43" s="6"/>
+      <c r="O43" s="6">
+        <v>69</v>
+      </c>
       <c r="P43" s="7">
         <v>11.889560439560441</v>
       </c>
@@ -7705,31 +7814,75 @@
       <c r="R43" s="8">
         <v>9.3499999999999996</v>
       </c>
-      <c r="S43" s="8"/>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
       <c r="T43" s="9">
         <v>0.057971014492753624</v>
       </c>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="U43" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.028985507246376812</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8118,7 +8271,9 @@
       <c r="N46" s="6">
         <v>110</v>
       </c>
-      <c r="O46" s="6"/>
+      <c r="O46" s="6">
+        <v>70</v>
+      </c>
       <c r="P46" s="7">
         <v>3.1669811320754717</v>
       </c>
@@ -8128,31 +8283,75 @@
       <c r="R46" s="8">
         <v>8.3869042857142855</v>
       </c>
-      <c r="S46" s="8"/>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
       <c r="T46" s="9">
         <v>0.2857142857142857</v>
       </c>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="U46" s="9">
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0.014285714285000001</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -9421,7 +9620,9 @@
       <c r="N55" s="6">
         <v>68</v>
       </c>
-      <c r="O55" s="6"/>
+      <c r="O55" s="6">
+        <v>52</v>
+      </c>
       <c r="P55" s="7">
         <v>3.9068070422535213</v>
       </c>
@@ -9431,31 +9632,75 @@
       <c r="R55" s="8">
         <v>38.469230769230769</v>
       </c>
-      <c r="S55" s="8"/>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
       <c r="T55" s="9">
         <v>0.019230769230769232</v>
       </c>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="U55" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.21153846153846154</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>11</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -10410,7 +10655,9 @@
       <c r="N62" s="6">
         <v>81</v>
       </c>
-      <c r="O62" s="6"/>
+      <c r="O62" s="6">
+        <v>52</v>
+      </c>
       <c r="P62" s="7">
         <v>3.0720879518072293</v>
       </c>
@@ -10420,31 +10667,75 @@
       <c r="R62" s="8">
         <v>4.8700000000000001</v>
       </c>
-      <c r="S62" s="8"/>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
       <c r="T62" s="9">
         <v>0.67307692307692313</v>
       </c>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="U62" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -11711,7 +12002,9 @@
       <c r="N71" s="6">
         <v>104</v>
       </c>
-      <c r="O71" s="6"/>
+      <c r="O71" s="6">
+        <v>56</v>
+      </c>
       <c r="P71" s="7">
         <v>4.5663303030303029</v>
       </c>
@@ -11721,31 +12014,75 @@
       <c r="R71" s="8">
         <v>5.1432092592592591</v>
       </c>
-      <c r="S71" s="8"/>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
       <c r="T71" s="9">
         <v>0.40000000000000002</v>
       </c>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="U71" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -12229,7 +12566,9 @@
       <c r="N75" s="6">
         <v>58</v>
       </c>
-      <c r="O75" s="6"/>
+      <c r="O75" s="6">
+        <v>25</v>
+      </c>
       <c r="P75" s="7">
         <v>4.6099421052631584</v>
       </c>
@@ -12239,31 +12578,75 @@
       <c r="R75" s="8">
         <v>4.6576374999999999</v>
       </c>
-      <c r="S75" s="8"/>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
       <c r="T75" s="9">
         <v>0.40000000000000002</v>
       </c>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="U75" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -14352,7 +14735,9 @@
       <c r="N90" s="6">
         <v>80</v>
       </c>
-      <c r="O90" s="6"/>
+      <c r="O90" s="6">
+        <v>54</v>
+      </c>
       <c r="P90" s="7">
         <v>7.8972912500000003</v>
       </c>
@@ -14362,31 +14747,75 @@
       <c r="R90" s="8">
         <v>15.317628846153847</v>
       </c>
-      <c r="S90" s="8"/>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
       <c r="T90" s="9">
         <v>0.07407407407407407</v>
       </c>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="U90" s="9">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>41</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>32</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>28</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -17101,7 +17530,9 @@
       <c r="N109" s="6">
         <v>114</v>
       </c>
-      <c r="O109" s="6"/>
+      <c r="O109" s="6">
+        <v>29</v>
+      </c>
       <c r="P109" s="7">
         <v>5.0401452173913048</v>
       </c>
@@ -17111,31 +17542,75 @@
       <c r="R109" s="8">
         <v>8.2580448275862075</v>
       </c>
-      <c r="S109" s="8"/>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
       <c r="T109" s="9">
         <v>0.20689655172413793</v>
       </c>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="U109" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -23025,7 +23500,9 @@
       <c r="N149" s="6">
         <v>129</v>
       </c>
-      <c r="O149" s="6"/>
+      <c r="O149" s="6">
+        <v>118</v>
+      </c>
       <c r="P149" s="7">
         <v>24.886466165413534</v>
       </c>
@@ -23035,31 +23512,75 @@
       <c r="R149" s="8">
         <v>62.44140927835052</v>
       </c>
-      <c r="S149" s="8"/>
+      <c r="S149" s="8">
+        <v>7</v>
+      </c>
       <c r="T149" s="9">
         <v>0.022988505747126436</v>
       </c>
-      <c r="U149" s="9"/>
-      <c r="V149" s="9"/>
-      <c r="W149" s="9"/>
-      <c r="X149" s="9"/>
-      <c r="Y149" s="9"/>
-      <c r="Z149" s="9"/>
-      <c r="AA149" s="9"/>
-      <c r="AB149" s="9"/>
-      <c r="AC149" s="9"/>
-      <c r="AD149" s="6"/>
-      <c r="AE149" s="6"/>
-      <c r="AF149" s="6"/>
-      <c r="AG149" s="6"/>
-      <c r="AH149" s="6"/>
-      <c r="AI149" s="6"/>
-      <c r="AJ149" s="6"/>
-      <c r="AK149" s="6"/>
-      <c r="AL149" s="6"/>
-      <c r="AM149" s="6"/>
-      <c r="AN149" s="9"/>
-      <c r="AO149" s="6"/>
+      <c r="U149" s="9">
+        <v>0.55084745762711862</v>
+      </c>
+      <c r="V149" s="9">
+        <v>0</v>
+      </c>
+      <c r="W149" s="9">
+        <v>0</v>
+      </c>
+      <c r="X149" s="9">
+        <v>0.0084745762711864406</v>
+      </c>
+      <c r="Y149" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="9">
+        <v>0.016949152542372881</v>
+      </c>
+      <c r="AB149" s="9">
+        <v>0.016949152542372881</v>
+      </c>
+      <c r="AC149" s="9">
+        <v>0.52542372881355937</v>
+      </c>
+      <c r="AD149" s="6">
+        <v>67</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>65</v>
+      </c>
+      <c r="AF149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH149" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK149" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL149" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM149" s="6">
+        <v>62</v>
+      </c>
+      <c r="AN149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO149" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP149" s="4">
         <v>58</v>
       </c>
@@ -24822,7 +25343,9 @@
       <c r="N162" s="6">
         <v>101</v>
       </c>
-      <c r="O162" s="6"/>
+      <c r="O162" s="6">
+        <v>33</v>
+      </c>
       <c r="P162" s="7">
         <v>8.9496567010309285</v>
       </c>
@@ -24832,31 +25355,75 @@
       <c r="R162" s="8">
         <v>3.5963531249999998</v>
       </c>
-      <c r="S162" s="8"/>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
       <c r="T162" s="9">
         <v>0.12121212121212122</v>
       </c>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="U162" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -26757,7 +27324,9 @@
       <c r="N175" s="6">
         <v>68</v>
       </c>
-      <c r="O175" s="6"/>
+      <c r="O175" s="6">
+        <v>35</v>
+      </c>
       <c r="P175" s="7">
         <v>7.505290476190476</v>
       </c>
@@ -26767,31 +27336,75 @@
       <c r="R175" s="8">
         <v>3.0247484848484847</v>
       </c>
-      <c r="S175" s="8"/>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
       <c r="T175" s="9">
         <v>0.2857142857142857</v>
       </c>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="U175" s="9">
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -26866,7 +27479,9 @@
       <c r="N176" s="6">
         <v>31</v>
       </c>
-      <c r="O176" s="6"/>
+      <c r="O176" s="6">
+        <v>16</v>
+      </c>
       <c r="P176" s="7">
         <v>2.9421875000000002</v>
       </c>
@@ -26876,31 +27491,75 @@
       <c r="R176" s="8">
         <v>7.8260437500000002</v>
       </c>
-      <c r="S176" s="8"/>
+      <c r="S176" s="8">
+        <v>7</v>
+      </c>
       <c r="T176" s="9">
         <v>0.3125</v>
       </c>
-      <c r="U176" s="9"/>
-      <c r="V176" s="9"/>
-      <c r="W176" s="9"/>
-      <c r="X176" s="9"/>
-      <c r="Y176" s="9"/>
-      <c r="Z176" s="9"/>
-      <c r="AA176" s="9"/>
-      <c r="AB176" s="9"/>
-      <c r="AC176" s="9"/>
-      <c r="AD176" s="6"/>
-      <c r="AE176" s="6"/>
-      <c r="AF176" s="6"/>
-      <c r="AG176" s="6"/>
-      <c r="AH176" s="6"/>
-      <c r="AI176" s="6"/>
-      <c r="AJ176" s="6"/>
-      <c r="AK176" s="6"/>
-      <c r="AL176" s="6"/>
-      <c r="AM176" s="6"/>
-      <c r="AN176" s="9"/>
-      <c r="AO176" s="6"/>
+      <c r="U176" s="9">
+        <v>0</v>
+      </c>
+      <c r="V176" s="9">
+        <v>0</v>
+      </c>
+      <c r="W176" s="9">
+        <v>0</v>
+      </c>
+      <c r="X176" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO176" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP176" s="4">
         <v>58</v>
       </c>
@@ -27444,7 +28103,9 @@
       <c r="N180" s="6">
         <v>40</v>
       </c>
-      <c r="O180" s="6"/>
+      <c r="O180" s="6">
+        <v>14</v>
+      </c>
       <c r="P180" s="7">
         <v>5.1273138888888887</v>
       </c>
@@ -27454,31 +28115,75 @@
       <c r="R180" s="8">
         <v>16.245235714285716</v>
       </c>
-      <c r="S180" s="8"/>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
       <c r="T180" s="9">
         <v>0.14285714285714285</v>
       </c>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="U180" s="9">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -28753,7 +29458,9 @@
       <c r="N189" s="6">
         <v>81</v>
       </c>
-      <c r="O189" s="6"/>
+      <c r="O189" s="6">
+        <v>70</v>
+      </c>
       <c r="P189" s="7">
         <v>5.5866259259259259</v>
       </c>
@@ -28763,31 +29470,75 @@
       <c r="R189" s="8">
         <v>28.181355932203392</v>
       </c>
-      <c r="S189" s="8"/>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
       <c r="T189" s="9">
         <v>0.27142857142857141</v>
       </c>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="U189" s="9">
+        <v>0.58571428571428574</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.15714285714285714</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.41428571428571431</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>48</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>41</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>29</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28864,7 +29615,9 @@
       <c r="N190" s="6">
         <v>65</v>
       </c>
-      <c r="O190" s="6"/>
+      <c r="O190" s="6">
+        <v>25</v>
+      </c>
       <c r="P190" s="7">
         <v>3.6816934426229508</v>
       </c>
@@ -28874,31 +29627,75 @@
       <c r="R190" s="8">
         <v>5.8902791666666667</v>
       </c>
-      <c r="S190" s="8"/>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
       <c r="T190" s="9">
         <v>0.76000000000000001</v>
       </c>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="U190" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -30386,7 +31183,9 @@
       <c r="N200" s="6">
         <v>25</v>
       </c>
-      <c r="O200" s="6"/>
+      <c r="O200" s="6">
+        <v>12</v>
+      </c>
       <c r="P200" s="7">
         <v>16.733332000000001</v>
       </c>
@@ -30396,31 +31195,75 @@
       <c r="R200" s="8">
         <v>3</v>
       </c>
-      <c r="S200" s="8"/>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
       <c r="T200" s="9">
         <v>0.16666666666666666</v>
       </c>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="U200" s="9">
+        <v>0</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -31009,7 +31852,9 @@
       <c r="N205" s="6">
         <v>45</v>
       </c>
-      <c r="O205" s="6"/>
+      <c r="O205" s="6">
+        <v>15</v>
+      </c>
       <c r="P205" s="7">
         <v>5.3948155555555548</v>
       </c>
@@ -31019,31 +31864,75 @@
       <c r="R205" s="8">
         <v>3.3066666666666666</v>
       </c>
-      <c r="S205" s="8"/>
+      <c r="S205" s="8">
+        <v>7</v>
+      </c>
       <c r="T205" s="9">
         <v>0.59999999999999998</v>
       </c>
-      <c r="U205" s="9"/>
-      <c r="V205" s="9"/>
-      <c r="W205" s="9"/>
-      <c r="X205" s="9"/>
-      <c r="Y205" s="9"/>
-      <c r="Z205" s="9"/>
-      <c r="AA205" s="9"/>
-      <c r="AB205" s="9"/>
-      <c r="AC205" s="9"/>
-      <c r="AD205" s="6"/>
-      <c r="AE205" s="6"/>
-      <c r="AF205" s="6"/>
-      <c r="AG205" s="6"/>
-      <c r="AH205" s="6"/>
-      <c r="AI205" s="6"/>
-      <c r="AJ205" s="6"/>
-      <c r="AK205" s="6"/>
-      <c r="AL205" s="6"/>
-      <c r="AM205" s="6"/>
-      <c r="AN205" s="9"/>
-      <c r="AO205" s="6"/>
+      <c r="U205" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V205" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="W205" s="9">
+        <v>0</v>
+      </c>
+      <c r="X205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD205" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF205" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK205" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO205" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP205" s="4">
         <v>58</v>
       </c>
@@ -31120,7 +32009,9 @@
       <c r="N206" s="6">
         <v>41</v>
       </c>
-      <c r="O206" s="6"/>
+      <c r="O206" s="6">
+        <v>21</v>
+      </c>
       <c r="P206" s="7">
         <v>10.616667441860466</v>
       </c>
@@ -31130,31 +32021,75 @@
       <c r="R206" s="8">
         <v>7.6212944444444446</v>
       </c>
-      <c r="S206" s="8"/>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
       <c r="T206" s="9">
         <v>0.2857142857142857</v>
       </c>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="U206" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0.047619047619000002</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
@@ -31195,7 +32130,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -31225,35 +32160,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>3244.71</v>
+      </c>
+      <c r="N207" s="6">
+        <v>36</v>
+      </c>
+      <c r="O207" s="6">
+        <v>21</v>
+      </c>
+      <c r="P207" s="7">
+        <v>7.234285714285714</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>20.996033333333333</v>
+      </c>
+      <c r="R207" s="8">
+        <v>7.3912714285714287</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
@@ -32252,52 +33245,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="AA216" s="11">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="AB216" s="11">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="AC216" s="11">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="AD216" s="11">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="AE216" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AF216" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AG216" s="11">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="AH216" s="11">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="AI216" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AJ216" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AK216" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AL216" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AM216" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -32314,10 +33307,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -935,25 +935,25 @@
     <t>214</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 8.869,39</t>
-  </si>
-  <si>
-    <t>94.2</t>
-  </si>
-  <si>
-    <t>62.9</t>
-  </si>
-  <si>
-    <t>6.10</t>
-  </si>
-  <si>
-    <t>22.1</t>
-  </si>
-  <si>
-    <t>9.9</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 8.851,06</t>
+  </si>
+  <si>
+    <t>94.1</t>
+  </si>
+  <si>
+    <t>62.8</t>
+  </si>
+  <si>
+    <t>6.11</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>10.0</t>
   </si>
   <si>
     <t>6.1</t>
@@ -962,7 +962,7 @@
     <t>30.8%</t>
   </si>
   <si>
-    <t>17.8%</t>
+    <t>17.9%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -980,7 +980,7 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.2%</t>
+    <t>6.3%</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -989,10 +989,10 @@
     <t>6.6%</t>
   </si>
   <si>
-    <t>2484.0</t>
-  </si>
-  <si>
-    <t>2031.0</t>
+    <t>2499.0</t>
+  </si>
+  <si>
+    <t>2044.0</t>
   </si>
   <si>
     <t>113.0</t>
@@ -1001,22 +1001,22 @@
     <t>29.0</t>
   </si>
   <si>
-    <t>416.0</t>
-  </si>
-  <si>
-    <t>141.0</t>
+    <t>418.0</t>
+  </si>
+  <si>
+    <t>142.0</t>
   </si>
   <si>
     <t>18.0</t>
   </si>
   <si>
-    <t>711.0</t>
+    <t>718.0</t>
   </si>
   <si>
     <t>287.0</t>
   </si>
   <si>
-    <t>749.0</t>
+    <t>754.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -16515,7 +16515,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16545,35 +16545,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>5551.2600000000002</v>
+      </c>
+      <c r="N102" s="6">
+        <v>66</v>
+      </c>
+      <c r="O102" s="6">
+        <v>46</v>
+      </c>
+      <c r="P102" s="7">
+        <v>7.2404411764705889</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>32.503260869565217</v>
+      </c>
+      <c r="R102" s="8">
+        <v>21.6470825</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.28260869565217389</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.15217391304347827</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -932,91 +932,91 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
   </si>
   <si>
-    <t>33</t>
+    <t>215</t>
   </si>
   <si>
-    <t>R$ 8.851,06</t>
+    <t>30</t>
   </si>
   <si>
-    <t>94.1</t>
+    <t>R$ 8.877,51</t>
   </si>
   <si>
-    <t>62.8</t>
+    <t>94.9</t>
   </si>
   <si>
-    <t>6.11</t>
+    <t>63.6</t>
   </si>
   <si>
-    <t>22.2</t>
+    <t>6.19</t>
+  </si>
+  <si>
+    <t>22.4</t>
   </si>
   <si>
     <t>10.0</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>30.8%</t>
+    <t>30.0%</t>
   </si>
   <si>
-    <t>17.9%</t>
+    <t>18.2%</t>
   </si>
   <si>
     <t>1.0%</t>
   </si>
   <si>
-    <t>0.3%</t>
+    <t>0.2%</t>
   </si>
   <si>
-    <t>3.7%</t>
+    <t>3.9%</t>
   </si>
   <si>
     <t>1.2%</t>
   </si>
   <si>
-    <t>0.2%</t>
+    <t>6.4%</t>
   </si>
   <si>
-    <t>6.3%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
+    <t>2.6%</t>
   </si>
   <si>
     <t>6.6%</t>
   </si>
   <si>
-    <t>2499.0</t>
+    <t>2650.0</t>
   </si>
   <si>
-    <t>2044.0</t>
+    <t>2178.0</t>
   </si>
   <si>
-    <t>113.0</t>
+    <t>115.0</t>
   </si>
   <si>
     <t>29.0</t>
   </si>
   <si>
-    <t>418.0</t>
+    <t>461.0</t>
   </si>
   <si>
-    <t>142.0</t>
+    <t>143.0</t>
   </si>
   <si>
-    <t>18.0</t>
+    <t>20.0</t>
   </si>
   <si>
-    <t>718.0</t>
+    <t>768.0</t>
   </si>
   <si>
-    <t>287.0</t>
+    <t>307.0</t>
   </si>
   <si>
-    <t>754.0</t>
+    <t>787.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -6471,7 +6471,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6501,35 +6501,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>16255.59</v>
+      </c>
+      <c r="N34" s="6">
+        <v>212</v>
+      </c>
+      <c r="O34" s="6">
+        <v>157</v>
+      </c>
+      <c r="P34" s="7">
+        <v>24.845631067961165</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>33.999893630573247</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.1344370860927153</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.15286624203821655</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.4140127388535032</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0.006369426751592357</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.28662420382165604</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.095541401273885357</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.10191082802547771</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>77</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>65</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>45</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>15</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -6727,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6757,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>7887.1099999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>108</v>
+      </c>
+      <c r="O36" s="6">
+        <v>93</v>
+      </c>
+      <c r="P36" s="7">
+        <v>3.941060909090909</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>41.359497849462365</v>
+      </c>
+      <c r="R36" s="8">
+        <v>31.056883695652171</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.18279569892473119</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0.021505376344086023</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>34</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>33</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>24</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -12687,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12715,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>10100.370000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>127</v>
+      </c>
+      <c r="O76" s="6">
+        <v>71</v>
+      </c>
+      <c r="P76" s="7">
+        <v>4.8177000000000003</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>29.245539436619719</v>
+      </c>
+      <c r="R76" s="8">
+        <v>16.145952857142856</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.29577464788732394</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.14084507042253522</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.042253521126760563</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>9</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -18561,33 +18735,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>38</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22328,7 +22548,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22358,35 +22578,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>6054.9099999999999</v>
+      </c>
+      <c r="N141" s="6">
+        <v>76</v>
+      </c>
+      <c r="O141" s="6">
+        <v>57</v>
+      </c>
+      <c r="P141" s="7">
+        <v>5.0230263157894735</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>17.383333333333333</v>
+      </c>
+      <c r="R141" s="8">
+        <v>4.1046789473684209</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.24561403508771928</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.070175438596491224</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33247,137 +33525,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>96</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
         <v>338</v>
       </c>
-      <c t="s" r="AY216" s="11">
+      <c t="s" r="AY217" s="11">
         <v>338</v>
       </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -938,31 +938,31 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
+    <t>29</t>
   </si>
   <si>
-    <t>R$ 8.877,51</t>
+    <t>R$ 8.923,57</t>
   </si>
   <si>
-    <t>94.9</t>
+    <t>95.3</t>
   </si>
   <si>
     <t>63.6</t>
   </si>
   <si>
-    <t>6.19</t>
+    <t>6.24</t>
   </si>
   <si>
-    <t>22.4</t>
+    <t>22.5</t>
   </si>
   <si>
-    <t>10.0</t>
+    <t>10.1</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>30.0%</t>
+    <t>30.1%</t>
   </si>
   <si>
     <t>18.2%</t>
@@ -25192,7 +25192,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25222,18 +25222,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>17444.720000000001</v>
+      </c>
+      <c r="N159" s="6">
+        <v>173</v>
+      </c>
       <c r="O159" s="6">
         <v>143</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>16.396666470588237</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>36.05492957746479</v>
+      </c>
+      <c r="R159" s="8">
+        <v>11.122262142857144</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.09154929577464789</v>
+      </c>
       <c r="U159" s="9">
         <v>0.083916083916083919</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -938,22 +938,22 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>28</t>
   </si>
   <si>
-    <t>R$ 8.923,57</t>
+    <t>R$ 8.905,80</t>
   </si>
   <si>
-    <t>95.3</t>
+    <t>95.1</t>
   </si>
   <si>
     <t>63.6</t>
   </si>
   <si>
-    <t>6.24</t>
+    <t>6.23</t>
   </si>
   <si>
-    <t>22.5</t>
+    <t>22.4</t>
   </si>
   <si>
     <t>10.1</t>
@@ -962,7 +962,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>30.1%</t>
+    <t>30.2%</t>
   </si>
   <si>
     <t>18.2%</t>
@@ -14776,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>5599.8500000000004</v>
+      </c>
+      <c r="N89" s="6">
+        <v>55</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>3.4818719298245613</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>20.337780000000002</v>
+      </c>
+      <c r="R89" s="8">
+        <v>13.054545454545455</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29200,7 +29212,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31908,7 +31920,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33541,7 +33553,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-09).xlsx
@@ -938,43 +938,43 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 8.905,80</t>
+    <t>R$ 8.876,59</t>
   </si>
   <si>
-    <t>95.1</t>
+    <t>94.6</t>
   </si>
   <si>
-    <t>63.6</t>
+    <t>64.0</t>
   </si>
   <si>
-    <t>6.23</t>
+    <t>6.35</t>
   </si>
   <si>
-    <t>22.4</t>
+    <t>22.7</t>
   </si>
   <si>
     <t>10.1</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>30.2%</t>
+    <t>29.9%</t>
   </si>
   <si>
-    <t>18.2%</t>
+    <t>18.0%</t>
   </si>
   <si>
-    <t>1.0%</t>
+    <t>0.9%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.9%</t>
+    <t>3.8%</t>
   </si>
   <si>
     <t>1.2%</t>
@@ -983,46 +983,43 @@
     <t>6.4%</t>
   </si>
   <si>
-    <t>2.6%</t>
+    <t>2.5%</t>
   </si>
   <si>
-    <t>6.6%</t>
+    <t>2706.0</t>
   </si>
   <si>
-    <t>2650.0</t>
+    <t>2232.0</t>
   </si>
   <si>
-    <t>2178.0</t>
+    <t>117.0</t>
   </si>
   <si>
-    <t>115.0</t>
+    <t>30.0</t>
   </si>
   <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>461.0</t>
+    <t>468.0</t>
   </si>
   <si>
     <t>143.0</t>
   </si>
   <si>
-    <t>20.0</t>
+    <t>21.0</t>
   </si>
   <si>
-    <t>768.0</t>
+    <t>799.0</t>
   </si>
   <si>
-    <t>307.0</t>
+    <t>314.0</t>
   </si>
   <si>
-    <t>787.0</t>
+    <t>793.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>49.0</t>
+    <t>51.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2209,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2236,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>13204.709999999999</v>
+      </c>
+      <c r="N6" s="6">
+        <v>126</v>
+      </c>
+      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.9124999999999996</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.688947368421053</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.896098936170213</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.51578947368421058</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9187,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9217,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1220.5999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>12</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.3694416666666669</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>35.646660000000004</v>
+      </c>
+      <c r="R51" s="8">
+        <v>23.06334</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10268,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>93</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.010752688171999999</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.021505376344086023</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24124,7 +24237,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24154,35 +24267,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>6397.3400000000001</v>
+      </c>
+      <c r="N151" s="6">
+        <v>66</v>
+      </c>
+      <c r="O151" s="6">
+        <v>58</v>
+      </c>
+      <c r="P151" s="7">
+        <v>7.0121212121212126</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>16.715805172413795</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.503869642857143</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.44827586206896552</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25006,7 +25177,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25036,35 +25207,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>7236.8400000000001</v>
+      </c>
+      <c r="N157" s="6">
+        <v>75</v>
+      </c>
+      <c r="O157" s="6">
+        <v>65</v>
+      </c>
+      <c r="P157" s="7">
+        <v>11.225555999999999</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>18.92512769230769</v>
+      </c>
+      <c r="R157" s="8">
+        <v>2.2182162790697677</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.52307692307692311</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0.061538461538461542</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0.061538461538461542</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>35</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>26</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25105,7 +25334,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,35 +25364,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>7468.1800000000003</v>
+      </c>
+      <c r="N158" s="6">
+        <v>71</v>
+      </c>
+      <c r="O158" s="6">
+        <v>53</v>
+      </c>
+      <c r="P158" s="7">
+        <v>11.71338028169014</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>26.263835849056605</v>
+      </c>
+      <c r="R158" s="8">
+        <v>8.1512584905660379</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.11320754716981132</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26138,7 +26425,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26168,35 +26455,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>12269.18</v>
+      </c>
+      <c r="N165" s="6">
+        <v>130</v>
+      </c>
+      <c r="O165" s="6">
+        <v>96</v>
+      </c>
+      <c r="P165" s="7">
+        <v>19.321930075187968</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>62.551215624999998</v>
+      </c>
+      <c r="R165" s="8">
+        <v>31.268750000000001</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.052083333333333336</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
@@ -33759,43 +34104,43 @@
         <v>324</v>
       </c>
       <c t="s" r="AC217" s="11">
+        <v>323</v>
+      </c>
+      <c t="s" r="AD217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD217" s="11">
+      <c t="s" r="AE217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE217" s="11">
+      <c t="s" r="AF217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF217" s="11">
+      <c t="s" r="AG217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG217" s="11">
+      <c t="s" r="AH217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH217" s="11">
+      <c t="s" r="AI217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI217" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ217" s="11">
+      <c t="s" r="AK217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK217" s="11">
+      <c t="s" r="AL217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL217" s="11">
+      <c t="s" r="AM217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM217" s="11">
+      <c t="s" r="AN217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN217" s="11">
+      <c t="s" r="AO217" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AO217" s="11">
-        <v>337</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -33812,10 +34157,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>
